--- a/public/docs/ImportGedungTemplate.xlsx
+++ b/public/docs/ImportGedungTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahwal\Documents\Template Exel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fauza\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1673C17D-8B15-48D8-8C00-BBD8AA5A59F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5683F6-15A9-4665-B881-B77D3AE04804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="20400" windowHeight="11835" xr2:uid="{71646216-010A-4135-B419-552B85AD5EBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{71646216-010A-4135-B419-552B85AD5EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Lokasi" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
     <t>JL.Rumah Sakit Empang</t>
   </si>
   <si>
-    <t>Lokasi</t>
-  </si>
-  <si>
     <t>nama kolom</t>
   </si>
   <si>
@@ -70,10 +67,13 @@
     <t>*Nama Gedung</t>
   </si>
   <si>
-    <t>*Wajib Diisi untuk nama gedungnya</t>
-  </si>
-  <si>
     <t>NOTE :BUKA BATAS PENGISIAN</t>
+  </si>
+  <si>
+    <t>*Wajib Diisi</t>
+  </si>
+  <si>
+    <t>Gedung</t>
   </si>
 </sst>
 </file>
@@ -84,30 +84,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -126,6 +102,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -192,28 +190,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,30 +524,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C04584E-E69B-44E2-B286-BAA57F5F99A3}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.140625" customWidth="1"/>
+    <col min="1" max="1" width="35.109375" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>12</v>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -566,62 +561,62 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>500</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3">
-        <v>50</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
-        <v>500</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
